--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10月予定表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="10月予定表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -816,7 +817,7 @@
         </is>
       </c>
       <c r="E8" s="31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>0</v>
@@ -845,7 +846,7 @@
         </is>
       </c>
       <c r="E9" s="31" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>0</v>
@@ -857,57 +858,86 @@
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="28" t="n"/>
+      <c r="A10" s="27" t="n"/>
       <c r="B10" s="29" t="inlineStr">
         <is>
+          <t>— 行動制限:看護記録の統一化(情報収集) —</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>【情報収集・開始】国の定める行動制限の基準(精神保健福祉法および関連告示・通知、診療報酬上の身体的拘束最小化の要件など)の情報収集を開始(10/3 在宅)。</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="30" t="inlineStr">
+        <is>
+          <t>看護記録統一化のミーティングは日時未定。決まり次第反映。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="28" t="n"/>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr"/>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>【第1週 合計】</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="9" t="inlineStr"/>
-      <c r="E11" s="11" t="n">
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="11" t="n">
         <v>7.5</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×1日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>第2週
 10/4〜10/10
@@ -916,59 +946,30 @@
 院内:10/4・6・9</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>【継続】機能追加・調整を継続。</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>詳細は今後確定。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>【継続+検討】依頼対応、他部署(栄養科等)の動画修正フォロー。加えて、入院動画のチェック項目・承認サイン運用を整理し、承認済みの証跡をカルテに添付する最終形態(資料添付か、一行確認記録か)を検討・決定する。</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>最終形態は未定。今後の検討課題として着手。</t>
         </is>
       </c>
     </row>
@@ -976,12 +977,12 @@
       <c r="A14" s="27" t="n"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>【再構築】当院に既存のものをもとにした再構築を継続。</t>
+          <t>【継続+検討】依頼対応、他部署(栄養科等)の動画修正フォロー。加えて、入院動画のチェック項目・承認サイン運用を整理し、承認済みの証跡をカルテに添付する最終形態(資料添付か、一行確認記録か)を検討・決定する。</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -997,7 +998,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>最終形態は未定。今後の検討課題として着手。</t>
         </is>
       </c>
     </row>
@@ -1005,12 +1006,12 @@
       <c r="A15" s="27" t="n"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>【継続】看護部からの返答内容をふまえ、必要ならIWGへの提出も含めて対応。</t>
+          <t>【再構築】当院に既存のものをもとにした再構築を継続。</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1019,7 +1020,7 @@
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="8" t="n">
         <v>0</v>
@@ -1034,12 +1035,12 @@
       <c r="A16" s="27" t="n"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>— 胃カメラ動画:再構築 —</t>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>【再構築開始】胃カメラ動画の再構築を10月より開始。システムへの掲載内容もあわせて検討。</t>
+          <t>【継続】看護部からの返答内容をふまえ、必要ならIWGへの提出も含めて対応。</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1055,7 +1056,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>9月は内容検討のみだったが、10月から動画本体の再構築に着手。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1063,83 +1064,141 @@
       <c r="A17" s="27" t="n"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t>— 胃カメラ動画:再構築 —</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>【再構築開始】胃カメラ動画の再構築を10月より開始。システムへの掲載内容もあわせて検討。</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>9月は内容検討のみだったが、10月から動画本体の再構築に着手。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
           <t>— RPA:ZOOM会議 —</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>【会議】10/6 10:30〜、RPAとのZOOM会議(院内)。</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="n">
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>— 行動制限:看護記録の統一化(情報収集) —</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>【情報収集】10/4(院内)に院内カルテの行動制限に関する記録(記載様式・項目・記載のばらつき)を情報収集。国の定める行動制限の基準の情報収集も継続(10/5・8 在宅)し、院内の記録と照らし合わせて統一化に向けた論点を整理。</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>看護記録統一化のミーティングは日時未定。決まり次第反映。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="9" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>【第2週 合計】</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr"/>
-      <c r="D19" s="9" t="inlineStr"/>
-      <c r="E19" s="11" t="n">
+      <c r="C21" s="9" t="inlineStr"/>
+      <c r="D21" s="9" t="inlineStr"/>
+      <c r="E21" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="F21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>第3週
 10/11〜10/17
@@ -1149,81 +1208,23 @@
 有休:10/12・13</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="27" t="n"/>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="27" t="n"/>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F22" s="8" t="n">
         <v>0</v>
@@ -1238,7 +1239,7 @@
       <c r="A23" s="27" t="n"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
@@ -1252,7 +1253,7 @@
         </is>
       </c>
       <c r="E23" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0</v>
@@ -1267,83 +1268,141 @@
       <c r="A24" s="27" t="n"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>③ 医療事故対策システム(新規)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>【再構築】</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="27" t="n"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/14のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n">
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>10/12・13は有休。</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="9" t="inlineStr"/>
-      <c r="B26" s="10" t="inlineStr">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>【第3週 合計】</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr"/>
-      <c r="D26" s="9" t="inlineStr"/>
-      <c r="E26" s="11" t="n">
+      <c r="C28" s="9" t="inlineStr"/>
+      <c r="D28" s="9" t="inlineStr"/>
+      <c r="E28" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="F28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×3日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>第4週
 10/18〜10/24
@@ -1352,81 +1411,23 @@
 院内:10/18・19・23・24</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="27" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="27" t="n"/>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>6</v>
       </c>
       <c r="F29" s="8" t="n">
         <v>0</v>
@@ -1441,83 +1442,141 @@
       <c r="A30" s="27" t="n"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>② 動画:入退院案内動画(修正)</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="27" t="n"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>③ 医療事故対策システム(新規)</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>【再構築】</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="27" t="n"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
           <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="F32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="F31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="9" t="inlineStr"/>
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="11" t="n">
+      <c r="C34" s="9" t="inlineStr"/>
+      <c r="D34" s="9" t="inlineStr"/>
+      <c r="E34" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="12" t="inlineStr">
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1527,81 +1586,23 @@
 有休:10/30</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="27" t="n"/>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>0</v>
@@ -1616,7 +1617,7 @@
       <c r="A36" s="27" t="n"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -1630,7 +1631,7 @@
         </is>
       </c>
       <c r="E36" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>0</v>
@@ -1645,12 +1646,12 @@
       <c r="A37" s="27" t="n"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備:システム作成 —</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応】10/27のSW会議に向けたシステム対応。</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1659,14 +1660,14 @@
         </is>
       </c>
       <c r="E37" s="8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1674,132 +1675,165 @@
       <c r="A38" s="27" t="n"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="27" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>— SW会議準備:システム作成 —</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>【依頼対応】10/27のSW会議に向けたシステム対応。</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>依頼がなければ工数は減る見込み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="27" t="n"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="28" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>10/30は有休。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="B40" s="10" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="inlineStr"/>
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr"/>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="11" t="n">
+      <c r="C42" s="9" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="F42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="13" t="inlineStr"/>
-      <c r="B41" s="14" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="13" t="inlineStr"/>
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr"/>
-      <c r="E41" s="15" t="n">
+      <c r="C43" s="13" t="inlineStr"/>
+      <c r="D43" s="13" t="inlineStr"/>
+      <c r="E43" s="15" t="n">
         <v>135</v>
       </c>
-      <c r="F41" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="F43" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 = 135.0時間(残業なし・暫定)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="19" t="n"/>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="19" t="n"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B45" s="18" t="n"/>
@@ -1812,7 +1846,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B46" s="18" t="n"/>
@@ -1825,7 +1859,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -1835,21 +1869,61 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="19" t="n"/>
     </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="19" t="n"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="19" t="n"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>・行動制限:看護記録の統一化ミーティング — 日時未定。決まり次第、予定表に反映。</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="19" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A33:A39"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A43:G43"/>
+  <mergeCells count="14">
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="A8:A11"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A3:F5"/>
     <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A29:A33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -882,7 +882,7 @@
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
-          <t>看護記録統一化のミーティングは日時未定。決まり次第反映。</t>
+          <t>看護記録統一化のミーティングは10/9 10:00〜(院内)。</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0</v>
@@ -1143,62 +1143,91 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>看護記録統一化のミーティングは日時未定。決まり次第反映。</t>
+          <t>10/9のミーティングに向けて、院内記録と国の基準の比較資料を準備。</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="28" t="n"/>
+      <c r="A20" s="27" t="n"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
+          <t>— 行動制限:看護記録統一化ミーティング —</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>【会議】10/9 10:00〜、行動制限の看護記録の統一化についてのミーティング(院内)。情報収集した内容をもとに論点を共有。</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="28" t="n"/>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="9" t="inlineStr"/>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="9" t="inlineStr"/>
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>【第2週 合計】</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr"/>
-      <c r="D21" s="9" t="inlineStr"/>
-      <c r="E21" s="11" t="n">
+      <c r="C22" s="9" t="inlineStr"/>
+      <c r="D22" s="9" t="inlineStr"/>
+      <c r="E22" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>第3週
 10/11〜10/17
@@ -1208,52 +1237,23 @@
 有休:10/12・13</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n">
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="27" t="n"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F23" s="8" t="n">
         <v>0</v>
@@ -1268,12 +1268,12 @@
       <c r="A24" s="27" t="n"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1297,12 +1297,12 @@
       <c r="A25" s="27" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>0</v>
@@ -1326,83 +1326,112 @@
       <c r="A26" s="27" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="27" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/14のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n">
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="F28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>10/12・13は有休。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="9" t="inlineStr"/>
-      <c r="B28" s="10" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="inlineStr"/>
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>【第3週 合計】</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="11" t="n">
+      <c r="C29" s="9" t="inlineStr"/>
+      <c r="D29" s="9" t="inlineStr"/>
+      <c r="E29" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="inlineStr">
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×3日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>第4週
 10/18〜10/24
@@ -1411,52 +1440,23 @@
 院内:10/18・19・23・24</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>5</v>
       </c>
       <c r="F30" s="8" t="n">
         <v>0</v>
@@ -1471,12 +1471,12 @@
       <c r="A31" s="27" t="n"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="E31" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="8" t="n">
         <v>0</v>
@@ -1500,83 +1500,112 @@
       <c r="A32" s="27" t="n"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
+          <t>③ 医療事故対策システム(新規)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>【再構築】</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
           <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="9" t="inlineStr"/>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="F34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="9" t="inlineStr"/>
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="11" t="n">
+      <c r="C35" s="9" t="inlineStr"/>
+      <c r="D35" s="9" t="inlineStr"/>
+      <c r="E35" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="F35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1586,52 +1615,23 @@
 有休:10/30</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F36" s="8" t="n">
         <v>0</v>
@@ -1646,12 +1646,12 @@
       <c r="A37" s="27" t="n"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -1675,12 +1675,12 @@
       <c r="A38" s="27" t="n"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E38" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       <c r="A39" s="27" t="n"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備:システム作成 —</t>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応】10/27のSW会議に向けたシステム対応。</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1718,14 +1718,14 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       <c r="A40" s="27" t="n"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>— コア会議まとめ作成 —</t>
+          <t>— SW会議準備:システム作成 —</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+          <t>【依頼対応】10/27のSW会議に向けたシステム対応。</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -1754,99 +1754,115 @@
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼がなければ工数は減る見込み。</t>
         </is>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="28" t="n"/>
+      <c r="A41" s="27" t="n"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>— コア会議まとめ作成 —</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="F42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
         <is>
           <t>10/30は有休。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="9" t="inlineStr"/>
-      <c r="B42" s="10" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="9" t="inlineStr"/>
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="11" t="n">
+      <c r="C43" s="9" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="F43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="13" t="inlineStr"/>
-      <c r="B43" s="14" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="13" t="inlineStr"/>
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr"/>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="15" t="n">
+      <c r="C44" s="13" t="inlineStr"/>
+      <c r="D44" s="13" t="inlineStr"/>
+      <c r="E44" s="15" t="n">
         <v>135</v>
       </c>
-      <c r="F43" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="F44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 = 135.0時間(残業なし・暫定)</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="19" t="n"/>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B46" s="18" t="n"/>
@@ -1859,7 +1875,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B47" s="18" t="n"/>
@@ -1872,7 +1888,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B48" s="18" t="n"/>
@@ -1885,7 +1901,7 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B49" s="18" t="n"/>
@@ -1898,7 +1914,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>・行動制限:看護記録の統一化ミーティング — 日時未定。決まり次第、予定表に反映。</t>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -1908,22 +1924,22 @@
       <c r="F50" s="18" t="n"/>
       <c r="G50" s="19" t="n"/>
     </row>
+    <row r="51" ht="16" customHeight="1"/>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A35:A41"/>
+  <mergeCells count="13">
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A30:A34"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A36:A42"/>
+    <mergeCell ref="A23:A28"/>
     <mergeCell ref="A46:G46"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A29:A33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A13:A20"/>
-    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -875,14 +875,14 @@
         </is>
       </c>
       <c r="E10" s="31" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
-          <t>看護記録統一化のミーティングは10/9 10:00〜(院内)。</t>
+          <t>10/3は2時間30分残業(20:00終了・在宅)。看護記録統一化のミーティングは10/9 14:00〜(院内)。</t>
         </is>
       </c>
     </row>
@@ -925,14 +925,14 @@
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="9" t="inlineStr"/>
       <c r="E12" s="11" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>【労務判定】所定内(7.5h×1日・残業なし)</t>
+          <t>【労務判定】残業あり(10/3に2時間30分・在宅)</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>【会議】10/9 10:00〜、行動制限の看護記録の統一化についてのミーティング(院内)。情報収集した内容をもとに論点を共有。</t>
+          <t>【会議】10/9 14:00〜、行動制限の看護記録の統一化についてのミーティング(院内)。情報収集した内容をもとに論点を共有。</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1847,14 +1847,14 @@
       <c r="C44" s="13" t="inlineStr"/>
       <c r="D44" s="13" t="inlineStr"/>
       <c r="E44" s="15" t="n">
-        <v>135</v>
+        <v>137.5</v>
       </c>
       <c r="F44" s="15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>7.5時間 × 日勤18日 = 135.0時間(残業なし・暫定)</t>
+          <t>7.5時間 × 日勤18日 + 残業2.5時間(10/3・在宅)= 137.5時間(暫定)</t>
         </is>
       </c>
     </row>
@@ -1931,14 +1931,14 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A30:A34"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A36:A42"/>
     <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A23:A28"/>
     <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A36:A42"/>
-    <mergeCell ref="A23:A28"/>
     <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -754,7 +754,6 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -808,7 +807,7 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>【継続】9月からの続き。追加対応・調整を継続。</t>
+          <t>【継続】9月からの続き。10/3(在宅)に追加・修正を実施。</t>
         </is>
       </c>
       <c r="D8" s="31" t="inlineStr">
@@ -817,14 +816,14 @@
         </is>
       </c>
       <c r="E8" s="31" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G8" s="30" t="inlineStr">
         <is>
-          <t>詳細は今後確定。</t>
+          <t>10/3は1時間15分残業(在宅・20:00終了)。</t>
         </is>
       </c>
     </row>
@@ -875,14 +874,14 @@
         </is>
       </c>
       <c r="E10" s="31" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="F10" s="31" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="G10" s="30" t="inlineStr">
         <is>
-          <t>10/3は2時間30分残業(20:00終了・在宅)。看護記録統一化のミーティングは10/9 14:00〜(院内)。</t>
+          <t>10/3は1時間15分残業(在宅・20:00終了)。看護記録統一化のミーティングは10/9 14:00〜(院内)。</t>
         </is>
       </c>
     </row>
@@ -932,7 +931,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>【労務判定】残業あり(10/3に2時間30分・在宅)</t>
+          <t>【労務判定】残業あり(10/3に2時間30分・在宅/①健診センター1時間15分+行動制限1時間15分)</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1857,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -961,7 +962,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0</v>
@@ -1176,57 +1177,86 @@
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="28" t="n"/>
+      <c r="A21" s="27" t="n"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>— SWシステム:バグ修正 —</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>【バグ修正】SW会議で使用しているシステムのバグ修正(10月から対応)。</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n">
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>5.5</v>
       </c>
-      <c r="F21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="9" t="inlineStr"/>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>【第2週 合計】</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr"/>
-      <c r="D22" s="9" t="inlineStr"/>
-      <c r="E22" s="11" t="n">
+      <c r="C23" s="9" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" ht="34" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>第3週
 10/11〜10/17
@@ -1236,52 +1266,23 @@
 有休:10/12・13</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n">
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0</v>
@@ -1296,12 +1297,12 @@
       <c r="A25" s="27" t="n"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1325,12 +1326,12 @@
       <c r="A26" s="27" t="n"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1339,7 +1340,7 @@
         </is>
       </c>
       <c r="E26" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>0</v>
@@ -1354,83 +1355,141 @@
       <c r="A27" s="27" t="n"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="27" t="n"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/14のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n">
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="28" t="n"/>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="F28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="27" t="n"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>— SWシステム:バグ修正 —</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>【バグ修正】SW会議で使用しているシステムのバグ修正(10月から対応)。</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>10/12・13は有休。</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="9" t="inlineStr"/>
-      <c r="B29" s="10" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="9" t="inlineStr"/>
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>【第3週 合計】</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr"/>
-      <c r="D29" s="9" t="inlineStr"/>
-      <c r="E29" s="11" t="n">
+      <c r="C31" s="9" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="F29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×3日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>第4週
 10/18〜10/24
@@ -1439,81 +1498,23 @@
 院内:10/18・19・23・24</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>10</v>
-      </c>
-      <c r="F30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="27" t="n"/>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="27" t="n"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>6</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>0</v>
@@ -1528,83 +1529,170 @@
       <c r="A33" s="27" t="n"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>② 動画:入退院案内動画(修正)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="27" t="n"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>③ 医療事故対策システム(新規)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>【再構築】</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="27" t="n"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="28" t="n"/>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="F35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="27" t="n"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>— SWシステム:バグ修正 —</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>【バグ修正】SW会議で使用しているシステムのバグ修正(10月から対応)。</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="28" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="9" t="inlineStr"/>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="9" t="inlineStr"/>
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="11" t="n">
+      <c r="C38" s="9" t="inlineStr"/>
+      <c r="D38" s="9" t="inlineStr"/>
+      <c r="E38" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="F38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1614,110 +1702,23 @@
 有休:10/30</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>6</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="27" t="n"/>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="27" t="n"/>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>【継続】</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>2</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>0</v>
@@ -1732,12 +1733,12 @@
       <c r="A40" s="27" t="n"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備:システム作成 —</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応】10/27のSW会議に向けたシステム対応。</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -1746,14 +1747,14 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1761,145 +1762,194 @@
       <c r="A41" s="27" t="n"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
+          <t>③ 医療事故対策システム(新規)</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>【再構築】</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="27" t="n"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="27" t="n"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>— SW会議準備・システムのバグ修正 —</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>依頼がなければ工数は減る見込み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="27" t="n"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="28" t="n"/>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="F44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="28" t="n"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
         <is>
           <t>10/30は有休。</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="9" t="inlineStr"/>
-      <c r="B43" s="10" t="inlineStr">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="9" t="inlineStr"/>
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="11" t="n">
+      <c r="C46" s="9" t="inlineStr"/>
+      <c r="D46" s="9" t="inlineStr"/>
+      <c r="E46" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
+      <c r="F46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="13" t="inlineStr"/>
-      <c r="B44" s="14" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="13" t="inlineStr"/>
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="15" t="n">
+      <c r="C47" s="13" t="inlineStr"/>
+      <c r="D47" s="13" t="inlineStr"/>
+      <c r="E47" s="15" t="n">
         <v>137.5</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="F47" s="15" t="n">
         <v>2.5</v>
       </c>
-      <c r="G44" s="16" t="inlineStr">
+      <c r="G47" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 + 残業2.5時間(10/3・在宅)= 137.5時間(暫定)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B46" s="18" t="n"/>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="G46" s="19" t="n"/>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="n"/>
-      <c r="C47" s="18" t="n"/>
-      <c r="D47" s="18" t="n"/>
-      <c r="E47" s="18" t="n"/>
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="19" t="n"/>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="n"/>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="19" t="n"/>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B49" s="18" t="n"/>
@@ -1912,7 +1962,7 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B50" s="18" t="n"/>
@@ -1922,22 +1972,60 @@
       <c r="F50" s="18" t="n"/>
       <c r="G50" s="19" t="n"/>
     </row>
-    <row r="51" ht="16" customHeight="1"/>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="19" t="n"/>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A24:A30"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A32:A37"/>
+    <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A39:A45"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A47:G47"/>
     <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A36:A42"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -754,7 +754,6 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -962,7 +961,7 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="F13" s="8" t="n">
         <v>0</v>
@@ -982,7 +981,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>【継続+検討】依頼対応、他部署(栄養科等)の動画修正フォロー。加えて、入院動画のチェック項目・承認サイン運用を整理し、承認済みの証跡をカルテに添付する最終形態(資料添付か、一行確認記録か)を検討・決定する。</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -991,14 +990,14 @@
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>最終形態は未定。今後の検討課題として着手。</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1281,7 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" s="8" t="n">
         <v>0</v>
@@ -1302,7 +1301,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -1311,14 +1310,14 @@
         </is>
       </c>
       <c r="E25" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1513,7 @@
         </is>
       </c>
       <c r="E32" s="8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F32" s="8" t="n">
         <v>0</v>
@@ -1534,7 +1533,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1543,14 +1542,14 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1717,7 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>0</v>
@@ -1738,7 +1737,7 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -1747,14 +1746,14 @@
         </is>
       </c>
       <c r="E40" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F40" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2012,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A32:A37"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A32:A37"/>
-    <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A39:A45"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A49:G49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="E8" s="31" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="F8" s="31" t="n">
         <v>1.25</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>【継続】栄養科等、他の動画修正依頼への対応状況を確認しつつ継続。</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D9" s="31" t="inlineStr">
@@ -845,14 +845,14 @@
         </is>
       </c>
       <c r="E9" s="31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="31" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
@@ -2015,11 +2014,11 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A32:A37"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>【情報収集・開始】国の定める行動制限の基準(精神保健福祉法および関連告示・通知、診療報酬上の身体的拘束最小化の要件など)の情報収集を開始(10/3 在宅)。</t>
+          <t>【情報収集・開始】国の定める行動制限の基準(精神保健福祉法および関連告示・通知、診療報酬上の身体的拘束最小化の要件など)の情報収集を開始。あわせて院内のカルテ記録物(行動制限に関する記録)の情報収集を実施(10/3 在宅)。</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
@@ -2017,8 +2017,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>【情報収集・開始】国の定める行動制限の基準(精神保健福祉法および関連告示・通知、診療報酬上の身体的拘束最小化の要件など)の情報収集を開始。あわせて院内のカルテ記録物(行動制限に関する記録)の情報収集を実施(10/3 在宅)。</t>
+          <t>【情報収集・開始】国の定める行動制限の基準(精神保健福祉法および関連告示・通知、診療報酬上の身体的拘束最小化の要件など)の情報収集を開始(10/3 在宅)。</t>
         </is>
       </c>
       <c r="D10" s="31" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>【情報収集】10/4(院内)に院内カルテの行動制限に関する記録(記載様式・項目・記載のばらつき)を情報収集。国の定める行動制限の基準の情報収集も継続(10/5・8 在宅)し、院内の記録と照らし合わせて統一化に向けた論点を整理。</t>
+          <t>【情報収集】10/4(院内)に院内のカルテ記録物(行動制限に関する記録の記載様式・項目・記載のばらつき)を情報収集。国の定める行動制限の基準の情報収集も継続(10/5・8 在宅)し、院内の記録と照らし合わせて統一化に向けた論点を整理。</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -952,7 +952,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>【継続】機能追加・調整を継続。</t>
+          <t>【継続+検証】機能追加・調整を継続。10/6 13:00〜、宇井さんとシステムの検証(院内)。</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>詳細は今後確定。</t>
+          <t>10/6は午前にRPAのZOOM会議(10:30〜)、午後に宇井さんと検証(13:00〜)。</t>
         </is>
       </c>
     </row>
@@ -2017,8 +2017,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -732,7 +732,7 @@
         <is>
           <t>勤務日:日勤18日 × 7.5時間 = 135.0時間(残業は別途)
 日勤:10/3・4・5・6・8・9・14(コア会議)・15・17・18・19・20・23・24・25・27(スマートワーキング)・28(コア会議)・29
-在宅ワーク日(6日):10/3・5・8・17・20・29 / 院内勤務日(12日):10/4・6・9・14・15・18・19・23・24・25・27・28
+在宅ワーク日(7日):10/3・5・8・15・17・20・29 / 院内勤務日(11日):10/4・6・9・14・18・19・23・24・25・27・28
 有休:10/12・13・30 / 公休:10/1・2・7・10・11・16・21・22・26・31</t>
         </is>
       </c>
@@ -952,7 +952,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>【継続+検証】機能追加・調整を継続。10/6 13:00〜、宇井さんとシステムの検証(院内)。</t>
+          <t>【継続+検証+プレゼン】機能追加・調整を継続。10/6 13:00〜、宇井さんとシステムの検証(院内)。10/8(在宅)に追加・修正を行い、院内でPC14台へ同期。10/9 健診センターへプレゼン実施、修正・追加点あり。</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>10/6は午前にRPAのZOOM会議(10:30〜)、午後に宇井さんと検証(13:00〜)。</t>
+          <t>10/6は午前にRPAのZOOM会議(10:30〜)、午後に宇井さんと検証(13:00〜)。10/9プレゼンの修正・追加点は第3週に対応。</t>
         </is>
       </c>
     </row>
@@ -1260,8 +1260,8 @@
           <t>第3週
 10/11〜10/17
 (日勤3日 22.5h)
-在宅:10/17
-院内:10/14(コア会議)・15
+在宅:10/15・17
+院内:10/14(コア会議)
 有休:10/12・13</t>
         </is>
       </c>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【修正・追加】10/9プレゼンで出た修正・追加点をシステムに反映(10/15 在宅)。</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/15は院内から在宅に変更。</t>
         </is>
       </c>
     </row>
@@ -2017,8 +2017,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A49:G49"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -754,6 +754,7 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -952,7 +953,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>【継続+検証+プレゼン】機能追加・調整を継続。10/6 13:00〜、宇井さんとシステムの検証(院内)。10/8(在宅)に追加・修正を行い、院内でPC14台へ同期。10/9 健診センターへプレゼン実施、修正・追加点あり。</t>
+          <t>【継続+検証+プレゼン】機能追加・調整を継続(10/5 在宅)。10/6 13:00〜、宇井さんとシステムの検証(院内)。10/8は在宅で追加・修正を行った後、病院へ移動し健診センターシステムのPC14台へインストール・同期を実施。10/9 健診センターへプレゼン実施、修正・追加点あり。</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -961,14 +962,14 @@
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>11.5</v>
+        <v>13.25</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>10/6は午前にRPAのZOOM会議(10:30〜)、午後に宇井さんと検証(13:00〜)。10/9プレゼンの修正・追加点は第3週に対応。</t>
+          <t>10/5は1時間45分残業(在宅・21:00終了)。10/6は午前にRPAのZOOM会議(10:30〜)、午後に宇井さんと検証(13:00〜)。10/9プレゼンの修正・追加点は第3週に対応。</t>
         </is>
       </c>
     </row>
@@ -1135,14 +1136,14 @@
         </is>
       </c>
       <c r="E19" s="8" t="n">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>10/9のミーティングに向けて、院内記録と国の基準の比較資料を準備。</t>
+          <t>10/5は1時間45分残業(在宅・21:00終了)。10/9のミーティングに向けて、院内記録と国の基準の比較資料を準備。</t>
         </is>
       </c>
     </row>
@@ -1243,14 +1244,14 @@
       <c r="C23" s="9" t="inlineStr"/>
       <c r="D23" s="9" t="inlineStr"/>
       <c r="E23" s="11" t="n">
-        <v>37.5</v>
+        <v>41</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
+          <t>【労務判定】残業あり(10/5に3時間30分・在宅/①健診センター1時間45分+行動制限1時間45分)</t>
         </is>
       </c>
     </row>
@@ -1933,17 +1934,18 @@
       <c r="C47" s="13" t="inlineStr"/>
       <c r="D47" s="13" t="inlineStr"/>
       <c r="E47" s="15" t="n">
-        <v>137.5</v>
+        <v>141</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>7.5時間 × 日勤18日 + 残業2.5時間(10/3・在宅)= 137.5時間(暫定)</t>
-        </is>
-      </c>
-    </row>
+          <t>7.5時間 × 日勤18日 + 残業6.0時間(10/3に2時間30分・10/5に3時間30分、いずれも在宅)= 141.0時間(暫定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
@@ -2017,8 +2019,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A52:G52"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -731,7 +731,7 @@
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>勤務日:日勤18日 × 7.5時間 = 135.0時間(残業は別途)
-日勤:10/3・4・5・6・8・9・14(コア会議)・15・17・18・19・20・23・24・25・27(スマートワーキング)・28(コア会議)・29
+日勤:10/3・4・5・6・8・9・14(コア会議→中止)・15・17・18・19・20・23・24・25・27(スマートワーキング)・28(コア会議)・29
 在宅ワーク日(7日):10/3・5・8・15・17・20・29 / 院内勤務日(11日):10/4・6・9・14・18・19・23・24・25・27・28
 有休:10/12・13・30 / 公休:10/1・2・7・10・11・16・21・22・26・31</t>
         </is>
@@ -754,7 +754,6 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1262,7 +1261,7 @@
 10/11〜10/17
 (日勤3日 22.5h)
 在宅:10/15・17
-院内:10/14(コア会議)
+院内:10/14(コア会議は中止)
 有休:10/12・13</t>
         </is>
       </c>
@@ -1273,7 +1272,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>【修正・追加】10/9プレゼンで出た修正・追加点をシステムに反映(10/15 在宅)。</t>
+          <t>【修正・追加+実稼働チェック】10/9プレゼンで出た修正・追加点をシステムに反映(10/15 在宅・定時終了)。10/17(在宅)に健診センターシステムの実稼働チェック。</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1282,14 +1281,14 @@
         </is>
       </c>
       <c r="E24" s="8" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>10/15は院内から在宅に変更。</t>
+          <t>10/15は院内から在宅に変更(定時終了)。10/17は45分残業(在宅・19:00終了)。</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1388,7 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>【まとめ作成】10/14のコア会議の内容をまとめる(院内)。</t>
+          <t>【中止】10/14のコア会議は中止となったため、まとめ作成なし。</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1398,14 +1397,14 @@
         </is>
       </c>
       <c r="E28" s="8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F28" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1439,57 +1438,86 @@
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="28" t="n"/>
+      <c r="A30" s="27" t="n"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
+          <t>— 看護計画のシステム化(個人差対応) —</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>【立案・構築・モデル作成】個人差のある看護計画のシステム化について、立案・構築・モデル作成(10/17 在宅)。</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>10/17は45分残業(在宅・19:00終了)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n">
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>5.5</v>
       </c>
-      <c r="F30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="F31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
         <is>
           <t>10/12・13は有休。</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
-      <c r="B31" s="10" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="9" t="inlineStr"/>
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>【第3週 合計】</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="12" t="inlineStr">
-        <is>
-          <t>【労務判定】所定内(7.5h×3日・残業なし)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr"/>
+      <c r="D32" s="9" t="inlineStr"/>
+      <c r="E32" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>【労務判定】残業あり(10/17に1時間30分・在宅/①健診センター45分+看護計画45分)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>第4週
 10/18〜10/24
@@ -1498,59 +1526,30 @@
 院内:10/18・19・23・24</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>【継続】</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="27" t="n"/>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr">
-        <is>
-          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
-        </is>
-      </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1557,12 @@
       <c r="A34" s="27" t="n"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1572,14 +1571,14 @@
         </is>
       </c>
       <c r="E34" s="8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F34" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1586,12 @@
       <c r="A35" s="27" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1601,7 +1600,7 @@
         </is>
       </c>
       <c r="E35" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F35" s="8" t="n">
         <v>0</v>
@@ -1616,83 +1615,141 @@
       <c r="A36" s="27" t="n"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="27" t="n"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
           <t>— SWシステム:バグ修正 —</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>【バグ修正】SW会議で使用しているシステムのバグ修正(10月から対応)。</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="F37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="27" t="n"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>— 行動制限:看護記録の統一化(情報収集) —</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>【情報収集・仕分け】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>工数は①から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="28" t="n"/>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="9" t="inlineStr"/>
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="11" t="n">
+      <c r="C40" s="9" t="inlineStr"/>
+      <c r="D40" s="9" t="inlineStr"/>
+      <c r="E40" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F38" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
+      <c r="F40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1702,81 +1759,23 @@
 有休:10/30</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>9</v>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="27" t="n"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="27" t="n"/>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>③ 医療事故対策システム(新規)</t>
-        </is>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>【再構築】</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>3</v>
       </c>
       <c r="F41" s="8" t="n">
         <v>0</v>
@@ -1791,12 +1790,12 @@
       <c r="A42" s="27" t="n"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -1805,14 +1804,14 @@
         </is>
       </c>
       <c r="E42" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1819,12 @@
       <c r="A43" s="27" t="n"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備・システムのバグ修正 —</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
+          <t>【再構築】</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -1834,14 +1833,14 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1849,133 +1848,164 @@
       <c r="A44" s="27" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>【継続】</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="27" t="n"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>— SW会議準備・システムのバグ修正 —</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>依頼がなければ工数は減る見込み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="27" t="n"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
           <t>— コア会議まとめ作成 —</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="n">
+      <c r="D46" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>1.5</v>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="28" t="n"/>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="F46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="28" t="n"/>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="8" t="n">
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>10/30は有休。</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="9" t="inlineStr"/>
-      <c r="B46" s="10" t="inlineStr">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="9" t="inlineStr"/>
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr"/>
-      <c r="D46" s="9" t="inlineStr"/>
-      <c r="E46" s="11" t="n">
+      <c r="C48" s="9" t="inlineStr"/>
+      <c r="D48" s="9" t="inlineStr"/>
+      <c r="E48" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F46" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
+      <c r="F48" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="13" t="inlineStr"/>
-      <c r="B47" s="14" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="13" t="inlineStr"/>
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr"/>
-      <c r="D47" s="13" t="inlineStr"/>
-      <c r="E47" s="15" t="n">
-        <v>141</v>
-      </c>
-      <c r="F47" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>7.5時間 × 日勤18日 + 残業6.0時間(10/3に2時間30分・10/5に3時間30分、いずれも在宅)= 141.0時間(暫定)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr"/>
+      <c r="E49" s="15" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>7.5時間 × 日勤18日 + 残業7.5時間(10/3に2時間30分・10/5に3時間30分・10/17に1時間30分、いずれも在宅)= 142.5時間(暫定)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B49" s="18" t="n"/>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="19" t="n"/>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
-        </is>
-      </c>
-      <c r="B50" s="18" t="n"/>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="19" t="n"/>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B51" s="18" t="n"/>
@@ -1988,7 +2018,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
@@ -2001,7 +2031,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -2011,21 +2041,47 @@
       <c r="F53" s="18" t="n"/>
       <c r="G53" s="19" t="n"/>
     </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="19" t="n"/>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A32:A37"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A41:A47"/>
+    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A24:A30"/>
-    <mergeCell ref="A13:A22"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="A39:A45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -754,6 +754,7 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1591,7 +1592,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【再構築+資料整理】サイボウズ内に保存されている院内の事故報告書などの資料を整理し、再構築の土台にする。</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1607,7 +1608,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>サイボウズ内の事故報告書などの整理を開始。</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>【再構築】</t>
+          <t>【再構築+資料整理】サイボウズ内の事故報告書などの整理を継続し、整理した内容をもとに再構築を進める。</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -1840,7 +1841,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>整理の進み具合により11月へ継続。</t>
         </is>
       </c>
     </row>
@@ -2002,6 +2003,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
@@ -2072,8 +2074,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A33:A39"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A13:A22"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>【再構築+資料整理】サイボウズ内に保存されている院内の事故報告書などの資料を整理し、再構築の土台にする。</t>
+          <t>【再構築+資料整理】10/20(在宅)から、サイボウズ内に保存されている院内の事故報告書などの資料を整理し、再構築の土台にする。</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>サイボウズ内の事故報告書などの整理を開始。</t>
+          <t>サイボウズ内の事故報告書などの整理を10/20から開始。</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>【情報収集・仕分け】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。</t>
+          <t>【情報収集・仕分け・提出】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。10/19(院内)に看護記録の詳細を看護部へ渡した。</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1695,62 +1695,91 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>工数は①から振替。</t>
+          <t>看護部からの返答待ち。工数は①から振替。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="28" t="n"/>
+      <c r="A39" s="27" t="n"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
+          <t>— 看護計画のシステム化(個人差対応) —</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>【試作提出】10/19(院内)に個人差のある看護計画のシステム試作を看護部へ提出。</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>看護部からの返答待ち。工数は①から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="28" t="n"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="9" t="inlineStr"/>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="9" t="inlineStr"/>
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr"/>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="11" t="n">
+      <c r="C41" s="9" t="inlineStr"/>
+      <c r="D41" s="9" t="inlineStr"/>
+      <c r="E41" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="F41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1760,59 +1789,30 @@
 有休:10/30</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="27" t="n"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       <c r="A43" s="27" t="n"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>【再構築+資料整理】サイボウズ内の事故報告書などの整理を継続し、整理した内容をもとに再構築を進める。</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -1834,14 +1834,14 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>整理の進み具合により11月へ継続。</t>
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       <c r="A44" s="27" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【再構築+資料整理】サイボウズ内の事故報告書などの整理を継続し、整理した内容をもとに再構築を進める。</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -1863,14 +1863,14 @@
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>整理の進み具合により11月へ継続。</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       <c r="A45" s="27" t="n"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備・システムのバグ修正 —</t>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -1892,14 +1892,14 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       <c r="A46" s="27" t="n"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>— コア会議まとめ作成 —</t>
+          <t>— SW会議準備・システムのバグ修正 —</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -1928,99 +1928,115 @@
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼がなければ工数は減る見込み。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="28" t="n"/>
+      <c r="A47" s="27" t="n"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
+          <t>— コア会議まとめ作成 —</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="28" t="n"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="n">
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="F48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>10/30は有休。</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="9" t="inlineStr"/>
-      <c r="B48" s="10" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="9" t="inlineStr"/>
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr"/>
-      <c r="D48" s="9" t="inlineStr"/>
-      <c r="E48" s="11" t="n">
+      <c r="C49" s="9" t="inlineStr"/>
+      <c r="D49" s="9" t="inlineStr"/>
+      <c r="E49" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F48" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
+      <c r="F49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="13" t="inlineStr"/>
-      <c r="B49" s="14" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="13" t="inlineStr"/>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr"/>
-      <c r="E49" s="15" t="n">
+      <c r="C50" s="13" t="inlineStr"/>
+      <c r="D50" s="13" t="inlineStr"/>
+      <c r="E50" s="15" t="n">
         <v>142.5</v>
       </c>
-      <c r="F49" s="15" t="n">
+      <c r="F50" s="15" t="n">
         <v>7.5</v>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 + 残業7.5時間(10/3に2時間30分・10/5に3時間30分・10/17に1時間30分、いずれも在宅)= 142.5時間(暫定)</t>
         </is>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="n"/>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
-      <c r="G51" s="19" t="n"/>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
@@ -2033,7 +2049,7 @@
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -2046,7 +2062,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B54" s="18" t="n"/>
@@ -2059,7 +2075,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
@@ -2069,21 +2085,62 @@
       <c r="F55" s="18" t="n"/>
       <c r="G55" s="19" t="n"/>
     </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="19" t="n"/>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。返答待ち。</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="19" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A2:F2"/>
+  <mergeCells count="15">
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A33:A39"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A33:A40"/>
     <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A41:A47"/>
-    <mergeCell ref="A51:G51"/>
     <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A57:G57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -733,7 +733,7 @@
           <t>勤務日:日勤18日 × 7.5時間 = 135.0時間(残業は別途)
 日勤:10/3・4・5・6・8・9・14(コア会議→中止)・15・17・18・19・20・23・24・25・27(スマートワーキング)・28(コア会議)・29
 在宅ワーク日(7日):10/3・5・8・15・17・20・29 / 院内勤務日(11日):10/4・6・9・14・18・19・23・24・25・27・28
-有休:10/12・13・30 / 公休:10/1・2・7・10・11・16・21・22・26・31</t>
+公休(10日):10/1・2・7・10・11・12・13・16・21・22 / 有休(3日):10/26・30・31</t>
         </is>
       </c>
       <c r="B3" s="20" t="n"/>
@@ -754,7 +754,6 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1263,7 +1262,7 @@
 (日勤3日 22.5h)
 在宅:10/15・17
 院内:10/14(コア会議は中止)
-有休:10/12・13</t>
+公休:10/12・13</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -1492,7 +1491,7 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>10/12・13は有休。</t>
+          <t>10/12・13は公休。</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1542,7 @@
         </is>
       </c>
       <c r="E33" s="8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F33" s="8" t="n">
         <v>0</v>
@@ -1708,7 +1707,7 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>【試作提出】10/19(院内)に個人差のある看護計画のシステム試作を看護部へ提出。</t>
+          <t>【試作提出+文言追加】10/19(院内)に個人差のある看護計画のシステム試作を看護部へ提出。10/20(在宅)に看護計画の文言(言語)をさらに追加。</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -1717,7 +1716,7 @@
         </is>
       </c>
       <c r="E39" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39" s="8" t="n">
         <v>0</v>
@@ -1786,7 +1785,7 @@
 (日勤4日 30h)
 在宅:10/29
 院内:10/25・27(スマートワーキング)・28(コア会議)
-有休:10/30</t>
+有休:10/26・30・31</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -1986,7 +1985,7 @@
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>10/30は有休。</t>
+          <t>10/26・30・31は有休。</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2031,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
         <is>
@@ -2126,21 +2124,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A42:A48"/>
     <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A24:A31"/>
     <mergeCell ref="A33:A40"/>
     <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A57:G57"/>
     <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A57:G57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,7 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1583,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="34" customHeight="1">
+    <row r="35" ht="56" customHeight="1">
       <c r="A35" s="27" t="n"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
@@ -1591,7 +1592,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>【再構築+資料整理】10/20(在宅)から、サイボウズ内に保存されている院内の事故報告書などの資料を整理し、再構築の土台にする。</t>
+          <t>【再構築+資料整理】10/20(在宅)から、サイボウズ内に保存されている院内の事故報告書などの資料を整理し、再構築の土台にする。→10/23、サイボウズは入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -1607,7 +1608,7 @@
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>サイボウズ内の事故報告書などの整理を10/20から開始。</t>
+          <t>サイボウズ内の事故報告書などの整理を10/20から開始。10/23に保留。</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1670,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="96" customHeight="1">
       <c r="A38" s="27" t="n"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
@@ -1678,7 +1679,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>【情報収集・仕分け・提出】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。10/19(院内)に看護記録の詳細を看護部へ渡した。</t>
+          <t>【情報収集・仕分け・提出】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。10/19(院内)に看護記録の詳細を看護部へ渡した。10/23(院内)、看護記録のAI化に向けて、頓服・ECTなどの記録を一つずつ洗い出し、記録委員がひな型を作成する方針を看護部へ説明。看護会議で経緯・目的・やること・スケジュールを説明するよう依頼があり、説明資料を作成。</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1694,7 +1695,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>看護部からの返答待ち。工数は①から振替。</t>
+          <t>11/2 16:00〜 看護会議で説明、11/18 記録委員のひな型提出締め切り。工数は①から振替。</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1845,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
+    <row r="44" ht="52" customHeight="1">
       <c r="A44" s="27" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
@@ -1853,7 +1854,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>【再構築+資料整理】サイボウズ内の事故報告書などの整理を継続し、整理した内容をもとに再構築を進める。</t>
+          <t>【保留】サイボウズ内の事故報告書などの整理は保留(サイボウズに入っている内容の整理と、どんな入れ物がよいかの検討を行うことになったため)。</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -1862,14 +1863,14 @@
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>整理の進み具合により11月へ継続。</t>
+          <t>サイボウズの方針が決まり次第、再開。工数は行動制限(看護会議の準備)へ振替。</t>
         </is>
       </c>
     </row>
@@ -1961,93 +1962,110 @@
       </c>
     </row>
     <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="28" t="n"/>
+      <c r="A48" s="27" t="n"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>— 行動制限:看護記録の統一化(看護会議準備) —</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>【説明資料の仕上げ】11/2 16:00〜の看護会議に向けて、経緯・目的・やること・スケジュール(11/18 ひな型提出締め切り)の説明資料を仕上げる。</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>工数は③から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="28" t="n"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n">
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>10/26・30・31は有休。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="9" t="inlineStr"/>
-      <c r="B49" s="10" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="9" t="inlineStr"/>
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr"/>
-      <c r="D49" s="9" t="inlineStr"/>
-      <c r="E49" s="11" t="n">
+      <c r="C50" s="9" t="inlineStr"/>
+      <c r="D50" s="9" t="inlineStr"/>
+      <c r="E50" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="12" t="inlineStr">
+      <c r="F50" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="13" t="inlineStr"/>
-      <c r="B50" s="14" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="13" t="inlineStr"/>
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr"/>
-      <c r="D50" s="13" t="inlineStr"/>
-      <c r="E50" s="15" t="n">
+      <c r="C51" s="13" t="inlineStr"/>
+      <c r="D51" s="13" t="inlineStr"/>
+      <c r="E51" s="15" t="n">
         <v>142.5</v>
       </c>
-      <c r="F50" s="15" t="n">
+      <c r="F51" s="15" t="n">
         <v>7.5</v>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 + 残業7.5時間(10/3に2時間30分・10/5に3時間30分・10/17に1時間30分、いずれも在宅)= 142.5時間(暫定)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="17" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="n"/>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-      <c r="G52" s="19" t="n"/>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
@@ -2060,7 +2078,7 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B54" s="18" t="n"/>
@@ -2073,7 +2091,7 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
@@ -2086,7 +2104,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -2099,7 +2117,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
         </is>
       </c>
       <c r="B57" s="18" t="n"/>
@@ -2112,7 +2130,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。返答待ち。</t>
+          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
         </is>
       </c>
       <c r="B58" s="18" t="n"/>
@@ -2122,23 +2140,50 @@
       <c r="F58" s="18" t="n"/>
       <c r="G58" s="19" t="n"/>
     </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、記録委員がひな型を作成する方針に。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>・サイボウズ内の資料整理 — 10/23、サイボウズに入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="19" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A56:G56"/>
+  <mergeCells count="16">
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A42:A48"/>
     <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A54:G54"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A24:A31"/>
     <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A42:A49"/>
+    <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A3:F5"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A60:G60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>【情報収集・仕分け・提出】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。10/19(院内)に看護記録の詳細を看護部へ渡した。10/23(院内)、看護記録のAI化に向けて、頓服・ECTなどの記録を一つずつ洗い出し、記録委員がひな型を作成する方針を看護部へ説明。看護会議で経緯・目的・やること・スケジュールを説明するよう依頼があり、説明資料を作成。</t>
+          <t>【情報収集・仕分け・提出】10/18(院内)にカルテから各病棟の看護記録を情報収集し、ECT・頓服などの各記録に仕分け。10/19(院内)に看護記録の詳細を看護部へ渡した。10/23(院内)、看護記録のAI化に向けて、頓服・ECTなどの記録を一つずつ洗い出し、ひな型を作成する方針を看護部へ説明(ひな型の担当は後日決定)。看護会議で経緯・目的・やること・スケジュールを説明するよう依頼があり、説明資料を作成。</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>11/2 16:00〜 看護会議で説明、11/18 記録委員のひな型提出締め切り。工数は①から振替。</t>
+          <t>11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り(担当は後日決定)。工数は①から振替。</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、記録委員がひな型を作成する方針に。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
+          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、ひな型を作成する方針に(担当は後日決定)。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1729,57 +1729,86 @@
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="28" t="n"/>
+      <c r="A40" s="27" t="n"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
+          <t>— B2 行動制限チャートシステム:資料・案作成 —</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>【資料・案作成(開始)】10/24(院内)から、厚生労働省などのエビデンスに基づいたB2の行動制限チャートシステムの資料・案の作成に着手。</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>工数は⑤から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="28" t="n"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="9" t="inlineStr"/>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="9" t="inlineStr"/>
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>【第4週 合計】</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr"/>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="11" t="n">
+      <c r="C42" s="9" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="11" t="n">
         <v>37.5</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
+      <c r="F42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×5日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>第5週
 10/25〜10/31
@@ -1789,72 +1818,43 @@
 有休:10/26・30・31</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>① 健診センター予約システム(通過管理システムと統合)</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>【継続】月末時点の進捗確認。</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="27" t="n"/>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>② 動画:入退院案内動画(修正)</t>
-        </is>
-      </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="52" customHeight="1">
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
       <c r="A44" s="27" t="n"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>③ 医療事故対策システム(新規)</t>
+          <t>② 動画:入退院案内動画(修正)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>【保留】サイボウズ内の事故報告書などの整理は保留(サイボウズに入っている内容の整理と、どんな入れ物がよいかの検討を行うことになったため)。</t>
+          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -1870,20 +1870,20 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>サイボウズの方針が決まり次第、再開。工数は行動制限(看護会議の準備)へ振替。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="34" customHeight="1">
+          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="52" customHeight="1">
       <c r="A45" s="27" t="n"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
+          <t>③ 医療事故対策システム(新規)</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【保留】サイボウズ内の事故報告書などの整理は保留(サイボウズに入っている内容の整理と、どんな入れ物がよいかの検討を行うことになったため)。</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -1892,14 +1892,14 @@
         </is>
       </c>
       <c r="E45" s="8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>サイボウズの方針が決まり次第、再開。工数は行動制限(看護会議の準備)へ振替。</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       <c r="A46" s="27" t="n"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>— SW会議準備・システムのバグ修正 —</t>
+          <t>④ 看護部:申し送り要約AI(サマリー一式のAI化)</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
+          <t>【継続】</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -1921,14 +1921,14 @@
         </is>
       </c>
       <c r="E46" s="8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>依頼がなければ工数は減る見込み。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1936,12 @@
       <c r="A47" s="27" t="n"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>— コア会議まとめ作成 —</t>
+          <t>— SW会議準備・システムのバグ修正 —</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+          <t>【依頼対応・バグ修正】10/27のSW会議に向けたシステム対応と、SWシステムのバグ修正の継続。</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>依頼がなければ工数は減る見込み。</t>
         </is>
       </c>
     </row>
@@ -1965,133 +1965,165 @@
       <c r="A48" s="27" t="n"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
+          <t>— コア会議まとめ作成 —</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>【まとめ作成】10/28のコア会議の内容をまとめる(院内)。</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="27" t="n"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
           <t>— 行動制限:看護記録の統一化(看護会議準備) —</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>【説明資料の仕上げ】11/2 16:00〜の看護会議に向けて、経緯・目的・やること・スケジュール(11/18 ひな型提出締め切り)の説明資料を仕上げる。</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="8" t="n">
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="F49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>工数は③から振替。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="28" t="n"/>
-      <c r="B49" s="6" t="inlineStr">
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="27" t="n"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>— B2 行動制限チャートシステム:資料・案作成 —</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>【資料・案作成(継続)】厚生労働省などのエビデンスに基づき、B2の行動制限チャートシステムの資料・案の作成を継続。</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>工数は⑤から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>10/26・30・31は有休。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="9" t="inlineStr"/>
-      <c r="B50" s="10" t="inlineStr">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="9" t="inlineStr"/>
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr"/>
-      <c r="D50" s="9" t="inlineStr"/>
-      <c r="E50" s="11" t="n">
+      <c r="C52" s="9" t="inlineStr"/>
+      <c r="D52" s="9" t="inlineStr"/>
+      <c r="E52" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F50" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
+      <c r="F52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="13" t="inlineStr"/>
-      <c r="B51" s="14" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="13" t="inlineStr"/>
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr"/>
-      <c r="E51" s="15" t="n">
+      <c r="C53" s="13" t="inlineStr"/>
+      <c r="D53" s="13" t="inlineStr"/>
+      <c r="E53" s="15" t="n">
         <v>142.5</v>
       </c>
-      <c r="F51" s="15" t="n">
+      <c r="F53" s="15" t="n">
         <v>7.5</v>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G53" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 + 残業7.5時間(10/3に2時間30分・10/5に3時間30分・10/17に1時間30分、いずれも在宅)= 142.5時間(暫定)</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="n"/>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
-      <c r="G53" s="19" t="n"/>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
-        </is>
-      </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="19" t="n"/>
-    </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B55" s="18" t="n"/>
@@ -2104,7 +2136,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -2117,7 +2149,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B57" s="18" t="n"/>
@@ -2130,7 +2162,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B58" s="18" t="n"/>
@@ -2143,7 +2175,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、ひな型を作成する方針に(担当は後日決定)。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -2156,7 +2188,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>・サイボウズ内の資料整理 — 10/23、サイボウズに入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
+          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
         </is>
       </c>
       <c r="B60" s="18" t="n"/>
@@ -2166,15 +2198,40 @@
       <c r="F60" s="18" t="n"/>
       <c r="G60" s="19" t="n"/>
     </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、ひな型を作成する方針に(担当は後日決定)。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>・サイボウズ内の資料整理 — 10/23、サイボウズに入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A43:A51"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A53:G53"/>
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A24:A31"/>
     <mergeCell ref="A13:A22"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A33:A40"/>
-    <mergeCell ref="A42:A49"/>
     <mergeCell ref="A3:F5"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A58:G58"/>
@@ -2182,6 +2239,7 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A55:G55"/>
     <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A33:A41"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A60:G60"/>
   </mergeCells>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>【継続】</t>
+          <t>【継続+設定変更】10/23(院内)、健診センターシステムのSupabaseの登録メールアドレスを病院のメールアドレスに変更。</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -1732,12 +1732,12 @@
       <c r="A40" s="27" t="n"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>— B2 行動制限チャートシステム:資料・案作成 —</t>
+          <t>— B2病棟 行動制限チャートシステム:資料・案作成 —</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>【資料・案作成(開始)】10/24(院内)から、厚生労働省などのエビデンスに基づいたB2の行動制限チャートシステムの資料・案の作成に着手。</t>
+          <t>【資料・案作成(開始)】10/24(院内)から、厚生労働省などのエビデンスに基づいたB2病棟の行動制限チャートシステムの資料・案の作成に着手。</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2023,12 +2023,12 @@
       <c r="A50" s="27" t="n"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>— B2 行動制限チャートシステム:資料・案作成 —</t>
+          <t>— B2病棟 行動制限チャートシステム:資料・案作成 —</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>【資料・案作成(継続)】厚生労働省などのエビデンスに基づき、B2の行動制限チャートシステムの資料・案の作成を継続。</t>
+          <t>【資料・案作成(継続)】厚生労働省などのエビデンスに基づき、B2病棟の行動制限チャートシステムの資料・案の作成を継続。</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2226,22 +2226,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A43:A51"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A13:A22"/>
-    <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A33:A41"/>
     <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A33:A41"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="A24:A31"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A3:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>【継続】月末時点の進捗確認。</t>
+          <t>【継続+今後の流れ整理】月末時点の進捗確認。今後の流れ:①「子宮Aを通過管理に表示するか」と予約表の変更依頼が届いたら、まとめてシステムを修正 → ②修正したシステムを各PCへ手作業で導入(セキュリティのため) → ③全職員のアカウントを作成し、全員のログインを確認後にRLSのSQLを実行 → ④カルテNoの連携(患者CSV 約14万件の取込)。</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>変更依頼待ち。依頼が届き次第①から順に実施(11月以降)。</t>
         </is>
       </c>
     </row>
@@ -2224,24 +2224,38 @@
       <c r="F62" s="18" t="n"/>
       <c r="G62" s="19" t="n"/>
     </row>
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>・健診センター予約システム — 「子宮Aを通過管理に表示するか」と予約表の変更依頼待ち。届き次第、修正→各PCへ手作業で導入→全職員アカウント作成・ログイン確認→RLSのSQL実行→カルテNo連携(患者CSV 約14万件)の順に実施。</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="19" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A43:A51"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A13:A22"/>
+    <mergeCell ref="A24:A31"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A3:F5"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A58:G58"/>
     <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A43:A51"/>
-    <mergeCell ref="A8:A11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A62:G62"/>
     <mergeCell ref="A33:A41"/>
+    <mergeCell ref="A59:G59"/>
     <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A13:A22"/>
-    <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A3:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -691,7 +691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E43" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F43" s="8" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>【待機】動画自体は完了。追加システム・承認サイン等の依頼があれば対応。</t>
+          <t>【修正依頼対応】入退院案内動画の修正依頼あり(10/24)。依頼内容を確認し、修正に着手。</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -1863,14 +1863,14 @@
         </is>
       </c>
       <c r="E44" s="8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" s="8" t="n">
         <v>0</v>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>依頼時に施行予定(Wi-Fiが通じたら施行予定)。工数は①へ振替。</t>
+          <t>10/24に修正依頼あり。工数は①から振替。</t>
         </is>
       </c>
     </row>
@@ -2049,94 +2049,110 @@
       </c>
     </row>
     <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="28" t="n"/>
+      <c r="A51" s="27" t="n"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
+          <t>— 看護計画のシステム化(個人差対応) —</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>【情報収集】10/25(院内)に、個別性のある看護計画に向けてカルテ情報と記録情報を収集。</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>看護部からの試作への返答待ちと並行。工数は①・⑤から振替。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="28" t="n"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
           <t>⑤ その他(共通業務)</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>【毎日】老健・病院の補助金チェック、既存アプリの軽微な保守/【共通】定例ミーティング/【週末】予定表の実績反映・更新、11月分の仮予定表作成</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>10/26・30・31は有休。</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="9" t="inlineStr"/>
-      <c r="B52" s="10" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="9" t="inlineStr"/>
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>【第5週 合計】</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr"/>
-      <c r="D52" s="9" t="inlineStr"/>
-      <c r="E52" s="11" t="n">
+      <c r="C53" s="9" t="inlineStr"/>
+      <c r="D53" s="9" t="inlineStr"/>
+      <c r="E53" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="F52" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
+      <c r="F53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
         <is>
           <t>【労務判定】所定内(7.5h×4日・残業なし)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="13" t="inlineStr"/>
-      <c r="B53" s="14" t="inlineStr">
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="13" t="inlineStr"/>
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>【10月 月合計】</t>
         </is>
       </c>
-      <c r="C53" s="13" t="inlineStr"/>
-      <c r="D53" s="13" t="inlineStr"/>
-      <c r="E53" s="15" t="n">
+      <c r="C54" s="13" t="inlineStr"/>
+      <c r="D54" s="13" t="inlineStr"/>
+      <c r="E54" s="15" t="n">
         <v>142.5</v>
       </c>
-      <c r="F53" s="15" t="n">
+      <c r="F54" s="15" t="n">
         <v>7.5</v>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>7.5時間 × 日勤18日 + 残業7.5時間(10/3に2時間30分・10/5に3時間30分・10/17に1時間30分、いずれも在宅)= 142.5時間(暫定)</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>【保留・終了・待ち案件】</t>
-        </is>
-      </c>
-      <c r="B55" s="18" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
-      <c r="E55" s="18" t="n"/>
-      <c r="F55" s="18" t="n"/>
-      <c r="G55" s="19" t="n"/>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B56" s="18" t="n"/>
@@ -2149,7 +2165,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
+          <t>・看護部:音声入力システム — 院内Wi-Fi・スマホ未整備のため保留。工事終了後に再開。</t>
         </is>
       </c>
       <c r="B57" s="18" t="n"/>
@@ -2162,7 +2178,7 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
+          <t>・送迎アプリ — ベンダー導入のため開発対象から除外。</t>
         </is>
       </c>
       <c r="B58" s="18" t="n"/>
@@ -2175,7 +2191,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
+          <t>・BCP:災害時のコンピュータ室対応 — 8/15に石川さんよりヒアリング済み。今後広がるかは未定のため継続注視。</t>
         </is>
       </c>
       <c r="B59" s="18" t="n"/>
@@ -2188,7 +2204,7 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
+          <t>・栄養科:動画修正 — 返答待ち。返答が届き次第、内容を確認して着手。</t>
         </is>
       </c>
       <c r="B60" s="18" t="n"/>
@@ -2201,7 +2217,7 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、ひな型を作成する方針に(担当は後日決定)。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
+          <t>・看護計画のシステム化(個人差対応)— 10/19に試作を看護部へ提出。返答待ち。</t>
         </is>
       </c>
       <c r="B61" s="18" t="n"/>
@@ -2214,7 +2230,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>・サイボウズ内の資料整理 — 10/23、サイボウズに入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
+          <t>・行動制限:看護記録の統一化 — 10/19に看護記録の詳細を看護部へ渡した。10/23、ひな型を作成する方針に(担当は後日決定)。11/2 16:00〜 看護会議で説明、11/18 ひな型提出締め切り。</t>
         </is>
       </c>
       <c r="B62" s="18" t="n"/>
@@ -2227,7 +2243,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>・健診センター予約システム — 「子宮Aを通過管理に表示するか」と予約表の変更依頼待ち。届き次第、修正→各PCへ手作業で導入→全職員アカウント作成・ログイン確認→RLSのSQL実行→カルテNo連携(患者CSV 約14万件)の順に実施。</t>
+          <t>・サイボウズ内の資料整理 — 10/23、サイボウズに入っている内容の整理をし、どんな入れ物がよいか検討することになったため保留。</t>
         </is>
       </c>
       <c r="B63" s="18" t="n"/>
@@ -2237,11 +2253,24 @@
       <c r="F63" s="18" t="n"/>
       <c r="G63" s="19" t="n"/>
     </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>・健診センター予約システム — 「子宮Aを通過管理に表示するか」と予約表の変更依頼待ち。届き次第、修正→各PCへ手作業で導入→全職員アカウント作成・ログイン確認→RLSのSQL実行→カルテNo連携(患者CSV 約14万件)の順に実施。</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A43:A51"/>
     <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A43:A52"/>
     <mergeCell ref="A62:G62"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A24:A31"/>
@@ -2252,8 +2281,8 @@
     <mergeCell ref="A58:G58"/>
     <mergeCell ref="A56:G56"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A55:G55"/>
     <mergeCell ref="A33:A41"/>
+    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A57:G57"/>
   </mergeCells>

--- a/月ノルマ/月間週次予定表_2026年10月版.xlsx
+++ b/月ノルマ/月間週次予定表_2026年10月版.xlsx
@@ -754,7 +754,6 @@
       <c r="E5" s="25" t="n"/>
       <c r="F5" s="26" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
@@ -1854,7 +1853,7 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>【修正依頼対応】入退院案内動画の修正依頼あり(10/24)。依頼内容を確認し、修正に着手。</t>
+          <t>【修正依頼対応】10/24に修正依頼あり。修正内容:①入院のご案内に病院のロゴを入れ、「浅井病院 入院のご案内」と表示 ②表記を「患者様」から「患者さん」に変更。</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2148,7 +2147,6 @@
         </is>
       </c>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
         <is>
@@ -2268,23 +2266,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A56:G56"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="A43:A52"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A33:A41"/>
     <mergeCell ref="A13:A22"/>
     <mergeCell ref="A24:A31"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A3:F5"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A33:A41"/>
     <mergeCell ref="A64:G64"/>
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A3:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
